--- a/core/parser/src/test/resources/fixtures/synthetic/text-contrast.xlsx
+++ b/core/parser/src/test/resources/fixtures/synthetic/text-contrast.xlsx
@@ -70,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -78,6 +78,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -491,6 +493,20 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>theme on light fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>theme on dark fill</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
